--- a/artfynd/S 1920-2024 artfynd.xlsx
+++ b/artfynd/S 1920-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,43 +792,52 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128351086</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128351195</v>
+        <v>135570574</v>
       </c>
       <c r="B3" t="n">
-        <v>100160</v>
+        <v>104211</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1465</v>
+        <v>1910</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Borstsäv</t>
+          <t>Dvärglin</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Isolepis setacea</t>
+          <t>Radiola linoides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Roth</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -833,17 +847,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Flathult mot SV 2, Hl</t>
+          <t>Klackaberget, 800 m NNO, Hl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>380127</v>
+        <v>379672</v>
       </c>
       <c r="R3" t="n">
-        <v>6290619</v>
+        <v>6291305</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,14 +879,19 @@
           <t>Enslöv</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>N-Hal-2058</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,60 +904,68 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Skogsväg fukt grus</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Per Wahlén</t>
+          <t>Arne Lysell</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Wahlén</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Arne Lysell</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135570574</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128351231</v>
+        <v>135570580</v>
       </c>
       <c r="B4" t="n">
-        <v>100160</v>
+        <v>104211</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1465</v>
+        <v>1910</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Borstsäv</t>
+          <t>Dvärglin</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Isolepis setacea</t>
+          <t>Radiola linoides</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Roth</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -948,17 +975,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Flathult mot SV 3, Hl</t>
+          <t>Klackaberget, 820 m NNO, Hl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>380167</v>
+        <v>379685</v>
       </c>
       <c r="R4" t="n">
-        <v>6290492</v>
+        <v>6291308</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,14 +1007,19 @@
           <t>Enslöv</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>N-Hal-2059</t>
+        </is>
+      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,30 +1032,34 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Skogsväg fukt grus</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Per Wahlén</t>
+          <t>Arne Lysell</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Per Wahlén</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Arne Lysell</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135570580</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128503003</v>
+        <v>128351195</v>
       </c>
       <c r="B5" t="n">
-        <v>100159</v>
+        <v>100160</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1053,11 +1089,7 @@
           <t>50</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -1067,14 +1099,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Flathult mot SO (3), Hl</t>
+          <t>Flathult mot SV 2, Hl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>380167</v>
+        <v>380127</v>
       </c>
       <c r="R5" t="n">
-        <v>6290493</v>
+        <v>6290619</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,11 +1131,6 @@
           <t>Enslöv</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>N-Hal-1998</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
           <t>2025-09-09</t>
@@ -1124,10 +1151,15 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Skogsväg fukt grus</t>
+        </is>
+      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Arne Lysell</t>
+          <t>Per Wahlén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1135,40 +1167,41 @@
           <t>Per Wahlén</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128351195</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128351235</v>
+        <v>128351231</v>
       </c>
       <c r="B6" t="n">
-        <v>104132</v>
+        <v>100160</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1910</v>
+        <v>1465</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärglin</t>
+          <t>Borstsäv</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Radiola linoides</t>
+          <t>Isolepis setacea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Roth</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1255,43 +1288,52 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128351231</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128351248</v>
+        <v>128502997</v>
       </c>
       <c r="B7" t="n">
-        <v>104132</v>
+        <v>100237</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1910</v>
+        <v>1465</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärglin</t>
+          <t>Borstsäv</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Radiola linoides</t>
+          <t>Isolepis setacea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Roth</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -1301,17 +1343,17 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Flathult mot SV 4, Hl</t>
+          <t>Flathult mot SO (2), Hl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>380164</v>
+        <v>380137</v>
       </c>
       <c r="R7" t="n">
-        <v>6290450</v>
+        <v>6290609</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1331,6 +1373,11 @@
       <c r="W7" t="inlineStr">
         <is>
           <t>Enslöv</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>N-Hal-1997</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1353,73 +1400,85 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Skogsväg fukt grus</t>
-        </is>
-      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Arne Lysell</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
           <t>Per Wahlén</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Per Wahlén</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128502997</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112191548</v>
+        <v>128503003</v>
       </c>
       <c r="B8" t="n">
-        <v>98194</v>
+        <v>100159</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220686</v>
+        <v>1465</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Borstsäv</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Isolepis setacea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Trättebacken mot NNV, Hl</t>
+          <t>Flathult mot SO (3), Hl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>380415</v>
+        <v>380167</v>
       </c>
       <c r="R8" t="n">
-        <v>6290963</v>
+        <v>6290493</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,14 +1503,19 @@
           <t>Enslöv</t>
         </is>
       </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>N-Hal-1998</t>
+        </is>
+      </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,73 +1528,81 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Källsprång traktorväg</t>
-        </is>
-      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Arne Lysell</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
           <t>Per Wahlén</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Per Wahlén</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128503003</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112191560</v>
+        <v>135569805</v>
       </c>
       <c r="B9" t="n">
-        <v>98194</v>
+        <v>100237</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220686</v>
+        <v>1465</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Borstsäv</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Isolepis setacea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Trättebacken mot NNV2, Hl</t>
+          <t>Flathult mot SO (3), Hl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>380358</v>
+        <v>380169</v>
       </c>
       <c r="R9" t="n">
-        <v>6290774</v>
+        <v>6290488</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,14 +1627,24 @@
           <t>Enslöv</t>
         </is>
       </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>N-Hal-1998</t>
+        </is>
+      </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Växer i båda vägkanterna</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,25 +1657,515 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Källsprång traktorväg</t>
-        </is>
-      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Arne Lysell</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Arne Lysell</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135569805</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128351235</v>
+      </c>
+      <c r="B10" t="n">
+        <v>104132</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1910</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dvärglin</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Radiola linoides</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Roth</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Flathult mot SV 3, Hl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>380167</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6290492</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Enslöv</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Skogsväg fukt grus</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Per Wahlén</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Per Wahlén</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128351235</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128351248</v>
+      </c>
+      <c r="B11" t="n">
+        <v>104132</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1910</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dvärglin</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Radiola linoides</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Roth</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Flathult mot SV 4, Hl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>380164</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6290450</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Enslöv</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Skogsväg fukt grus</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Per Wahlén</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Per Wahlén</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128351248</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>112191548</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98194</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220686</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kambräken</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Blechnum spicant</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Trättebacken mot NNV, Hl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>380415</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6290963</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Enslöv</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-09-18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-09-18</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Källsprång traktorväg</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Per Wahlén</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Per Wahlén</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112191548</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>112191560</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98194</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220686</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kambräken</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Blechnum spicant</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Trättebacken mot NNV2, Hl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>380358</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6290774</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Enslöv</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-09-18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-09-18</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Källsprång traktorväg</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Per Wahlén</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Per Wahlén</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112191560</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 1920-2024 artfynd.xlsx
+++ b/artfynd/S 1920-2024 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>135570574</v>
       </c>
       <c r="B3" t="n">
-        <v>104211</v>
+        <v>104262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>135570580</v>
       </c>
       <c r="B4" t="n">
-        <v>104211</v>
+        <v>104262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>128502997</v>
       </c>
       <c r="B7" t="n">
-        <v>100237</v>
+        <v>100284</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>135569805</v>
       </c>
       <c r="B9" t="n">
-        <v>100237</v>
+        <v>100284</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 1920-2024 artfynd.xlsx
+++ b/artfynd/S 1920-2024 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>135570574</v>
       </c>
       <c r="B3" t="n">
-        <v>104262</v>
+        <v>104289</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>135570580</v>
       </c>
       <c r="B4" t="n">
-        <v>104262</v>
+        <v>104289</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>128502997</v>
       </c>
       <c r="B7" t="n">
-        <v>100284</v>
+        <v>100311</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>135569805</v>
       </c>
       <c r="B9" t="n">
-        <v>100284</v>
+        <v>100311</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 1920-2024 artfynd.xlsx
+++ b/artfynd/S 1920-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -800,40 +800,44 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128351195</v>
+        <v>135570574</v>
       </c>
       <c r="B3" t="n">
-        <v>100160</v>
+        <v>104294</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1465</v>
+        <v>1910</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Borstsäv</t>
+          <t>Dvärglin</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Isolepis setacea</t>
+          <t>Radiola linoides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Roth</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -843,17 +847,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Flathult mot SV 2, Hl</t>
+          <t>Klackaberget, 800 m NNO, Hl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>380127</v>
+        <v>379672</v>
       </c>
       <c r="R3" t="n">
-        <v>6290619</v>
+        <v>6291305</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,14 +879,19 @@
           <t>Enslöv</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>N-Hal-2058</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,65 +904,68 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Skogsväg fukt grus</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Per Wahlén</t>
+          <t>Arne Lysell</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Wahlén</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Arne Lysell</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128351195</t>
+          <t>https://artportalen.se/Sighting/135570574</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128351231</v>
+        <v>135570580</v>
       </c>
       <c r="B4" t="n">
-        <v>100160</v>
+        <v>104294</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1465</v>
+        <v>1910</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Borstsäv</t>
+          <t>Dvärglin</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Isolepis setacea</t>
+          <t>Radiola linoides</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Roth</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -963,17 +975,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Flathult mot SV 3, Hl</t>
+          <t>Klackaberget, 820 m NNO, Hl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>380167</v>
+        <v>379685</v>
       </c>
       <c r="R4" t="n">
-        <v>6290492</v>
+        <v>6291308</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,14 +1007,19 @@
           <t>Enslöv</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>N-Hal-2059</t>
+        </is>
+      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,35 +1032,34 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Skogsväg fukt grus</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Per Wahlén</t>
+          <t>Arne Lysell</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Per Wahlén</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Arne Lysell</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128351231</t>
+          <t>https://artportalen.se/Sighting/135570580</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128503003</v>
+        <v>128351195</v>
       </c>
       <c r="B5" t="n">
-        <v>100159</v>
+        <v>100160</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1073,11 +1089,7 @@
           <t>50</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -1087,14 +1099,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Flathult mot SO (3), Hl</t>
+          <t>Flathult mot SV 2, Hl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>380167</v>
+        <v>380127</v>
       </c>
       <c r="R5" t="n">
-        <v>6290493</v>
+        <v>6290619</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,11 +1131,6 @@
           <t>Enslöv</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>N-Hal-1998</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
           <t>2025-09-09</t>
@@ -1144,10 +1151,15 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Skogsväg fukt grus</t>
+        </is>
+      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Arne Lysell</t>
+          <t>Per Wahlén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1155,45 +1167,41 @@
           <t>Per Wahlén</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128503003</t>
+          <t>https://artportalen.se/Sighting/128351195</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128351235</v>
+        <v>128351231</v>
       </c>
       <c r="B6" t="n">
-        <v>104132</v>
+        <v>100160</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1910</v>
+        <v>1465</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärglin</t>
+          <t>Borstsäv</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Radiola linoides</t>
+          <t>Isolepis setacea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Roth</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1282,46 +1290,50 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128351235</t>
+          <t>https://artportalen.se/Sighting/128351231</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128351248</v>
+        <v>128502997</v>
       </c>
       <c r="B7" t="n">
-        <v>104132</v>
+        <v>100316</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1910</v>
+        <v>1465</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärglin</t>
+          <t>Borstsäv</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Radiola linoides</t>
+          <t>Isolepis setacea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Roth</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -1331,17 +1343,17 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Flathult mot SV 4, Hl</t>
+          <t>Flathult mot SO (2), Hl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>380164</v>
+        <v>380137</v>
       </c>
       <c r="R7" t="n">
-        <v>6290450</v>
+        <v>6290609</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1361,6 +1373,11 @@
       <c r="W7" t="inlineStr">
         <is>
           <t>Enslöv</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>N-Hal-1997</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1383,78 +1400,85 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Skogsväg fukt grus</t>
-        </is>
-      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Arne Lysell</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
           <t>Per Wahlén</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Per Wahlén</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128351248</t>
+          <t>https://artportalen.se/Sighting/128502997</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112191548</v>
+        <v>128503003</v>
       </c>
       <c r="B8" t="n">
-        <v>98194</v>
+        <v>100159</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220686</v>
+        <v>1465</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Borstsäv</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Isolepis setacea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Trättebacken mot NNV, Hl</t>
+          <t>Flathult mot SO (3), Hl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>380415</v>
+        <v>380167</v>
       </c>
       <c r="R8" t="n">
-        <v>6290963</v>
+        <v>6290493</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1479,14 +1503,19 @@
           <t>Enslöv</t>
         </is>
       </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>N-Hal-1998</t>
+        </is>
+      </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1499,78 +1528,81 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Källsprång traktorväg</t>
-        </is>
-      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Arne Lysell</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
           <t>Per Wahlén</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Per Wahlén</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112191548</t>
+          <t>https://artportalen.se/Sighting/128503003</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112191560</v>
+        <v>135569805</v>
       </c>
       <c r="B9" t="n">
-        <v>98194</v>
+        <v>100316</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220686</v>
+        <v>1465</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Borstsäv</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Isolepis setacea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Trättebacken mot NNV2, Hl</t>
+          <t>Flathult mot SO (3), Hl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>380358</v>
+        <v>380169</v>
       </c>
       <c r="R9" t="n">
-        <v>6290774</v>
+        <v>6290488</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1595,14 +1627,24 @@
           <t>Enslöv</t>
         </is>
       </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>N-Hal-1998</t>
+        </is>
+      </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Växer i båda vägkanterna</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1615,24 +1657,495 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Källsprång traktorväg</t>
-        </is>
-      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Arne Lysell</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Arne Lysell</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135569805</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128351235</v>
+      </c>
+      <c r="B10" t="n">
+        <v>104132</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1910</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dvärglin</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Radiola linoides</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Roth</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Flathult mot SV 3, Hl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>380167</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6290492</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Enslöv</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Skogsväg fukt grus</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Per Wahlén</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Per Wahlén</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="inlineStr">
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128351235</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128351248</v>
+      </c>
+      <c r="B11" t="n">
+        <v>104132</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1910</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dvärglin</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Radiola linoides</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Roth</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Flathult mot SV 4, Hl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>380164</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6290450</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Enslöv</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Skogsväg fukt grus</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Per Wahlén</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Per Wahlén</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128351248</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>112191548</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98194</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220686</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kambräken</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Blechnum spicant</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Trättebacken mot NNV, Hl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>380415</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6290963</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Enslöv</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-09-18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-09-18</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Källsprång traktorväg</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Per Wahlén</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Per Wahlén</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112191548</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>112191560</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98194</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220686</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kambräken</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Blechnum spicant</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Trättebacken mot NNV2, Hl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>380358</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6290774</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Enslöv</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-09-18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-09-18</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Källsprång traktorväg</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Per Wahlén</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Per Wahlén</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/112191560</t>
         </is>
@@ -1648,6 +2161,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 1920-2024 artfynd.xlsx
+++ b/artfynd/S 1920-2024 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>135570574</v>
       </c>
       <c r="B3" t="n">
-        <v>104294</v>
+        <v>104296</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>135570580</v>
       </c>
       <c r="B4" t="n">
-        <v>104294</v>
+        <v>104296</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>128502997</v>
       </c>
       <c r="B7" t="n">
-        <v>100316</v>
+        <v>100318</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>135569805</v>
       </c>
       <c r="B9" t="n">
-        <v>100316</v>
+        <v>100318</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 1920-2024 artfynd.xlsx
+++ b/artfynd/S 1920-2024 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>135570574</v>
       </c>
       <c r="B3" t="n">
-        <v>104296</v>
+        <v>104316</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>135570580</v>
       </c>
       <c r="B4" t="n">
-        <v>104296</v>
+        <v>104316</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>128502997</v>
       </c>
       <c r="B7" t="n">
-        <v>100318</v>
+        <v>100335</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>135569805</v>
       </c>
       <c r="B9" t="n">
-        <v>100318</v>
+        <v>100335</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 1920-2024 artfynd.xlsx
+++ b/artfynd/S 1920-2024 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>135570574</v>
       </c>
       <c r="B3" t="n">
-        <v>104316</v>
+        <v>104318</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>135570580</v>
       </c>
       <c r="B4" t="n">
-        <v>104316</v>
+        <v>104318</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>128502997</v>
       </c>
       <c r="B7" t="n">
-        <v>100335</v>
+        <v>100337</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>135569805</v>
       </c>
       <c r="B9" t="n">
-        <v>100335</v>
+        <v>100337</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 1920-2024 artfynd.xlsx
+++ b/artfynd/S 1920-2024 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>135570574</v>
       </c>
       <c r="B3" t="n">
-        <v>104318</v>
+        <v>104319</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>135570580</v>
       </c>
       <c r="B4" t="n">
-        <v>104318</v>
+        <v>104319</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>128502997</v>
       </c>
       <c r="B7" t="n">
-        <v>100337</v>
+        <v>100338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>135569805</v>
       </c>
       <c r="B9" t="n">
-        <v>100337</v>
+        <v>100338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
